--- a/exports/trend_1d/VOLTAS_full_report.xlsx
+++ b/exports/trend_1d/VOLTAS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:U73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>11.19</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42118</v>
+        <v>42121</v>
       </c>
       <c r="H2" t="n">
-        <v>279.89</v>
+        <v>265.45</v>
       </c>
       <c r="I2" t="n">
         <v>274.5014738766212</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K2" t="n">
-        <v>10.43</v>
+        <v>4.73</v>
       </c>
       <c r="L2" t="n">
         <v>3.29</v>
@@ -555,7 +578,7 @@
         <v>4.42</v>
       </c>
       <c r="N2" t="n">
-        <v>4.9</v>
+        <v>5.16</v>
       </c>
       <c r="O2" t="n">
         <v>2.3</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>15.1</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42145</v>
+        <v>42146</v>
       </c>
       <c r="H3" t="n">
-        <v>288.55</v>
+        <v>318.89</v>
       </c>
       <c r="I3" t="n">
         <v>305.5235536031987</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" t="n">
-        <v>-8.699999999999999</v>
+        <v>-20.13</v>
       </c>
       <c r="L3" t="n">
-        <v>12.49</v>
+        <v>20.93</v>
       </c>
       <c r="M3" t="n">
-        <v>1.48</v>
+        <v>3.99</v>
       </c>
       <c r="N3" t="n">
-        <v>5.39</v>
+        <v>10.51</v>
       </c>
       <c r="O3" t="n">
         <v>-5.16</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>14.1</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42184</v>
+        <v>42185</v>
       </c>
       <c r="H4" t="n">
-        <v>328.95</v>
+        <v>315.3</v>
       </c>
       <c r="I4" t="n">
         <v>322.5395794293605</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K4" t="n">
-        <v>3.15</v>
+        <v>-1.13</v>
       </c>
       <c r="L4" t="n">
         <v>5.91</v>
       </c>
       <c r="M4" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="N4" t="n">
         <v>5.51</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>13.07</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42297</v>
+        <v>42298</v>
       </c>
       <c r="H5" t="n">
-        <v>282.3</v>
+        <v>288.14</v>
       </c>
       <c r="I5" t="n">
         <v>285.3312670338213</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K5" t="n">
-        <v>10.47</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>4.79</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>10.86</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42317</v>
+        <v>42318</v>
       </c>
       <c r="H6" t="n">
-        <v>276.25</v>
+        <v>264.8</v>
       </c>
       <c r="I6" t="n">
         <v>266.5197422797813</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.13</v>
+        <v>-8.1</v>
       </c>
       <c r="L6" t="n">
-        <v>7.3</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="M6" t="n">
         <v>2.74</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>14.54</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42335</v>
+        <v>42338</v>
       </c>
       <c r="H7" t="n">
-        <v>282.7</v>
+        <v>288.5</v>
       </c>
       <c r="I7" t="n">
         <v>287.2019920107942</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.76</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>9.23</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M7" t="n">
         <v>0.93</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.29</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42375</v>
+        <v>42376</v>
       </c>
       <c r="H8" t="n">
-        <v>305.7</v>
+        <v>288.15</v>
       </c>
       <c r="I8" t="n">
         <v>295.8373078917302</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K8" t="n">
-        <v>5.96</v>
+        <v>-0.12</v>
       </c>
       <c r="L8" t="n">
         <v>3.81</v>
@@ -897,7 +992,7 @@
         <v>1.28</v>
       </c>
       <c r="N8" t="n">
-        <v>3.9</v>
+        <v>5.74</v>
       </c>
       <c r="O8" t="n">
         <v>2.05</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>12.52</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42446</v>
+        <v>42447</v>
       </c>
       <c r="H9" t="n">
-        <v>252.4</v>
+        <v>269.1</v>
       </c>
       <c r="I9" t="n">
         <v>264.7050078691933</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K9" t="n">
-        <v>12.41</v>
+        <v>6.61</v>
       </c>
       <c r="L9" t="n">
         <v>5.19</v>
@@ -954,7 +1061,7 @@
         <v>3.63</v>
       </c>
       <c r="N9" t="n">
-        <v>5.09</v>
+        <v>6.62</v>
       </c>
       <c r="O9" t="n">
         <v>-5.74</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>15.49</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42677</v>
+        <v>42678</v>
       </c>
       <c r="H10" t="n">
-        <v>364.85</v>
+        <v>360.05</v>
       </c>
       <c r="I10" t="n">
         <v>364.3211646337434</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K10" t="n">
-        <v>35.58</v>
+        <v>33.8</v>
       </c>
       <c r="L10" t="n">
         <v>6.97</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>153</v>
+        <v>154</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>9</v>
+      </c>
+      <c r="U10" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>11.11</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42739</v>
+        <v>42740</v>
       </c>
       <c r="H11" t="n">
-        <v>335.8</v>
+        <v>344.45</v>
       </c>
       <c r="I11" t="n">
         <v>338.4934681473646</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K11" t="n">
-        <v>6.74</v>
+        <v>4.33</v>
       </c>
       <c r="L11" t="n">
         <v>2.9</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42758</v>
+        <v>42759</v>
       </c>
       <c r="H12" t="n">
-        <v>338.2</v>
+        <v>324.2</v>
       </c>
       <c r="I12" t="n">
         <v>327.1660140912977</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.81</v>
+        <v>-5.88</v>
       </c>
       <c r="L12" t="n">
-        <v>3.22</v>
+        <v>6.23</v>
       </c>
       <c r="M12" t="n">
         <v>0.44</v>
       </c>
       <c r="N12" t="n">
-        <v>2.61</v>
+        <v>4.14</v>
       </c>
       <c r="O12" t="n">
         <v>2.58</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>11.5</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42786</v>
+        <v>42787</v>
       </c>
       <c r="H13" t="n">
-        <v>349.75</v>
+        <v>362.8</v>
       </c>
       <c r="I13" t="n">
         <v>352.2090431546995</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.88</v>
+        <v>-11.91</v>
       </c>
       <c r="L13" t="n">
-        <v>9.16</v>
+        <v>12.43</v>
       </c>
       <c r="M13" t="n">
         <v>3.22</v>
       </c>
       <c r="N13" t="n">
-        <v>3.28</v>
+        <v>3.73</v>
       </c>
       <c r="O13" t="n">
         <v>-4.14</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>10.02</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42872</v>
+        <v>42873</v>
       </c>
       <c r="H14" t="n">
-        <v>430.2</v>
+        <v>414.1</v>
       </c>
       <c r="I14" t="n">
         <v>414.9692576298983</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K14" t="n">
-        <v>18.58</v>
+        <v>14.14</v>
       </c>
       <c r="L14" t="n">
         <v>3.6</v>
       </c>
       <c r="M14" t="n">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="N14" t="n">
-        <v>2.22</v>
+        <v>3.74</v>
       </c>
       <c r="O14" t="n">
         <v>3.73</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>8.35</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42878</v>
+        <v>42879</v>
       </c>
       <c r="H15" t="n">
-        <v>409.85</v>
+        <v>446.5</v>
       </c>
       <c r="I15" t="n">
         <v>441.5264905415365</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
-        <v>1.03</v>
+        <v>-7.82</v>
       </c>
       <c r="L15" t="n">
-        <v>3.12</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>4.43</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4</v>
+        <v>8.94</v>
       </c>
       <c r="O15" t="n">
         <v>-3.74</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>10.9</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42909</v>
+        <v>42913</v>
       </c>
       <c r="H16" t="n">
-        <v>454.3</v>
+        <v>446.05</v>
       </c>
       <c r="I16" t="n">
         <v>453.4561060259933</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K16" t="n">
-        <v>1.75</v>
+        <v>-0.1</v>
       </c>
       <c r="L16" t="n">
         <v>5.24</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>9.99</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42934</v>
+        <v>42935</v>
       </c>
       <c r="H17" t="n">
-        <v>485.55</v>
+        <v>493.75</v>
       </c>
       <c r="I17" t="n">
         <v>486.1255933865583</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K17" t="n">
-        <v>-8.859999999999999</v>
+        <v>-10.69</v>
       </c>
       <c r="L17" t="n">
-        <v>10.07</v>
+        <v>11.07</v>
       </c>
       <c r="M17" t="n">
         <v>0.92</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.58</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H18" t="n">
-        <v>515.25</v>
+        <v>509.65</v>
       </c>
       <c r="I18" t="n">
         <v>510.6106814322283</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K18" t="n">
-        <v>4.35</v>
+        <v>3.22</v>
       </c>
       <c r="L18" t="n">
         <v>1.95</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43035</v>
+        <v>43038</v>
       </c>
       <c r="H19" t="n">
-        <v>542.4</v>
+        <v>559.8</v>
       </c>
       <c r="I19" t="n">
         <v>552.8471560875773</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.43</v>
+        <v>-9.84</v>
       </c>
       <c r="L19" t="n">
-        <v>7.11</v>
+        <v>10.17</v>
       </c>
       <c r="M19" t="n">
         <v>1.24</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43117</v>
+        <v>43118</v>
       </c>
       <c r="H20" t="n">
-        <v>628.25</v>
+        <v>600.45</v>
       </c>
       <c r="I20" t="n">
         <v>606.7217733799816</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K20" t="n">
-        <v>12.23</v>
+        <v>7.26</v>
       </c>
       <c r="L20" t="n">
         <v>3.26</v>
@@ -1581,7 +1820,7 @@
         <v>1.33</v>
       </c>
       <c r="N20" t="n">
-        <v>3.41</v>
+        <v>4.42</v>
       </c>
       <c r="O20" t="n">
         <v>3.21</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>12.11</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43166</v>
+        <v>43167</v>
       </c>
       <c r="H21" t="n">
-        <v>626.6</v>
+        <v>630.95</v>
       </c>
       <c r="I21" t="n">
         <v>629.3370427264596</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.36</v>
+        <v>-5.08</v>
       </c>
       <c r="L21" t="n">
         <v>6.39</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.93</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43231</v>
+        <v>43234</v>
       </c>
       <c r="H22" t="n">
-        <v>618</v>
+        <v>596.15</v>
       </c>
       <c r="I22" t="n">
         <v>600.0787905270893</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.05</v>
+        <v>-5.52</v>
       </c>
       <c r="L22" t="n">
         <v>6.32</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>10.17</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43301</v>
+        <v>43304</v>
       </c>
       <c r="H23" t="n">
-        <v>552.95</v>
+        <v>573.75</v>
       </c>
       <c r="I23" t="n">
         <v>558.8188192918315</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K23" t="n">
-        <v>7.25</v>
+        <v>3.76</v>
       </c>
       <c r="L23" t="n">
         <v>3.33</v>
       </c>
       <c r="M23" t="n">
-        <v>1.26</v>
+        <v>2.18</v>
       </c>
       <c r="N23" t="n">
-        <v>3.69</v>
+        <v>3.76</v>
       </c>
       <c r="O23" t="n">
         <v>-3.54</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>10.41</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43353</v>
+        <v>43354</v>
       </c>
       <c r="H24" t="n">
-        <v>583.3</v>
+        <v>575.6</v>
       </c>
       <c r="I24" t="n">
         <v>579.6178489230452</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K24" t="n">
-        <v>1.66</v>
+        <v>0.32</v>
       </c>
       <c r="L24" t="n">
         <v>2.81</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>10.59</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43418</v>
+        <v>43419</v>
       </c>
       <c r="H25" t="n">
-        <v>542.35</v>
+        <v>553</v>
       </c>
       <c r="I25" t="n">
         <v>549.9201175942956</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K25" t="n">
-        <v>5.78</v>
+        <v>3.93</v>
       </c>
       <c r="L25" t="n">
         <v>8.050000000000001</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>12.71</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43508</v>
+        <v>43509</v>
       </c>
       <c r="H26" t="n">
-        <v>522.3</v>
+        <v>507.5</v>
       </c>
       <c r="I26" t="n">
         <v>518.9307006375135</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.55</v>
+        <v>-8.23</v>
       </c>
       <c r="L26" t="n">
-        <v>7.22</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="M26" t="n">
         <v>2.47</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>10.67</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43523</v>
+        <v>43524</v>
       </c>
       <c r="H27" t="n">
-        <v>542.95</v>
+        <v>566.55</v>
       </c>
       <c r="I27" t="n">
         <v>558.7944852903134</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.99</v>
+        <v>-11.64</v>
       </c>
       <c r="L27" t="n">
-        <v>9.82</v>
+        <v>12.41</v>
       </c>
       <c r="M27" t="n">
         <v>0.71</v>
       </c>
       <c r="N27" t="n">
-        <v>1.47</v>
+        <v>4.35</v>
       </c>
       <c r="O27" t="n">
         <v>-2.83</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.12</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43592</v>
+        <v>43593</v>
       </c>
       <c r="H28" t="n">
-        <v>601.45</v>
+        <v>576.65</v>
       </c>
       <c r="I28" t="n">
         <v>589.3250381741746</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K28" t="n">
-        <v>6.16</v>
+        <v>1.78</v>
       </c>
       <c r="L28" t="n">
         <v>4.42</v>
@@ -2037,7 +2372,7 @@
         <v>2.03</v>
       </c>
       <c r="N28" t="n">
-        <v>2.63</v>
+        <v>4.12</v>
       </c>
       <c r="O28" t="n">
         <v>4.35</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>9.19</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43622</v>
+        <v>43623</v>
       </c>
       <c r="H29" t="n">
-        <v>588.5</v>
+        <v>617.2</v>
       </c>
       <c r="I29" t="n">
         <v>605.7683692730307</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.05</v>
+        <v>-7.03</v>
       </c>
       <c r="L29" t="n">
-        <v>5.18</v>
+        <v>7.34</v>
       </c>
       <c r="M29" t="n">
         <v>2.23</v>
       </c>
       <c r="N29" t="n">
-        <v>3.19</v>
+        <v>4.88</v>
       </c>
       <c r="O29" t="n">
         <v>-4.12</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,25 +2489,25 @@
         <v>11.7</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H30" t="n">
-        <v>615.65</v>
+        <v>603.5</v>
       </c>
       <c r="I30" t="n">
         <v>609.4669966202096</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.25</v>
+        <v>-2.22</v>
       </c>
       <c r="L30" t="n">
         <v>4.97</v>
       </c>
       <c r="M30" t="n">
-        <v>0.5</v>
+        <v>3.98</v>
       </c>
       <c r="N30" t="n">
         <v>3.04</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>7.81</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43682</v>
+        <v>43683</v>
       </c>
       <c r="H31" t="n">
-        <v>601.65</v>
+        <v>617.8</v>
       </c>
       <c r="I31" t="n">
         <v>615.6993399272163</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K31" t="n">
-        <v>0.31</v>
+        <v>-2.37</v>
       </c>
       <c r="L31" t="n">
-        <v>1.96</v>
+        <v>2.87</v>
       </c>
       <c r="M31" t="n">
         <v>0.91</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>10.14</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43816</v>
+        <v>43817</v>
       </c>
       <c r="H32" t="n">
-        <v>669.05</v>
+        <v>654.15</v>
       </c>
       <c r="I32" t="n">
         <v>663.7007188492544</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K32" t="n">
-        <v>8.300000000000001</v>
+        <v>5.88</v>
       </c>
       <c r="L32" t="n">
         <v>6.26</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>8.51</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43839</v>
+        <v>43840</v>
       </c>
       <c r="H33" t="n">
-        <v>684.3</v>
+        <v>687.5</v>
       </c>
       <c r="I33" t="n">
         <v>687.3725910206037</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.61</v>
+        <v>-5.1</v>
       </c>
       <c r="L33" t="n">
-        <v>5.35</v>
+        <v>5.76</v>
       </c>
       <c r="M33" t="n">
         <v>0.65</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>6.36</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43889</v>
+        <v>43892</v>
       </c>
       <c r="H34" t="n">
-        <v>678.75</v>
+        <v>664.1</v>
       </c>
       <c r="I34" t="n">
         <v>673.0827590645384</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.27</v>
+        <v>-3.4</v>
       </c>
       <c r="L34" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="M34" t="n">
         <v>1.47</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>11.99</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H35" t="n">
-        <v>480.15</v>
+        <v>539.8</v>
       </c>
       <c r="I35" t="n">
         <v>516.9439880318184</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K35" t="n">
-        <v>27.7</v>
+        <v>18.72</v>
       </c>
       <c r="L35" t="n">
         <v>4.95</v>
       </c>
       <c r="M35" t="n">
-        <v>3.67</v>
+        <v>5.38</v>
       </c>
       <c r="N35" t="n">
-        <v>5.51</v>
+        <v>12.42</v>
       </c>
       <c r="O35" t="n">
         <v>-2.16</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>17.05</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44279</v>
+        <v>44280</v>
       </c>
       <c r="H36" t="n">
-        <v>984.8</v>
+        <v>958.6</v>
       </c>
       <c r="I36" t="n">
         <v>975.7489196505389</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K36" t="n">
-        <v>82.44</v>
+        <v>77.58</v>
       </c>
       <c r="L36" t="n">
         <v>6.26</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>208</v>
+        <v>209</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>10</v>
+      </c>
+      <c r="U36" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>12.31</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44348</v>
+        <v>44349</v>
       </c>
       <c r="H37" t="n">
-        <v>1013.2</v>
+        <v>1034.4</v>
       </c>
       <c r="I37" t="n">
         <v>1030.997124664326</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.7</v>
+        <v>-7.91</v>
       </c>
       <c r="L37" t="n">
-        <v>7.86</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M37" t="n">
         <v>1.59</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>8.31</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44365</v>
+        <v>44368</v>
       </c>
       <c r="H38" t="n">
-        <v>1029.3</v>
+        <v>1019.15</v>
       </c>
       <c r="I38" t="n">
         <v>1019.790673152465</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.49</v>
+        <v>-1.47</v>
       </c>
       <c r="L38" t="n">
         <v>3.11</v>
       </c>
       <c r="M38" t="n">
-        <v>0.48</v>
+        <v>1.15</v>
       </c>
       <c r="N38" t="n">
         <v>3.16</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>8.24</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44439</v>
+        <v>44440</v>
       </c>
       <c r="H39" t="n">
-        <v>995.85</v>
+        <v>1045.8</v>
       </c>
       <c r="I39" t="n">
         <v>1034.261344054106</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K39" t="n">
-        <v>2.29</v>
+        <v>-2.61</v>
       </c>
       <c r="L39" t="n">
         <v>5.96</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>1.32</v>
       </c>
       <c r="N39" t="n">
-        <v>2.92</v>
+        <v>5.02</v>
       </c>
       <c r="O39" t="n">
         <v>-0.99</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>9.24</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44489</v>
+        <v>44490</v>
       </c>
       <c r="H40" t="n">
-        <v>1247.6</v>
+        <v>1192.05</v>
       </c>
       <c r="I40" t="n">
         <v>1237.176746237106</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K40" t="n">
-        <v>19.3</v>
+        <v>13.98</v>
       </c>
       <c r="L40" t="n">
         <v>4</v>
       </c>
       <c r="M40" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="N40" t="n">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="O40" t="n">
         <v>5.02</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>11.42</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44567</v>
+        <v>44568</v>
       </c>
       <c r="H41" t="n">
-        <v>1249.8</v>
+        <v>1270.9</v>
       </c>
       <c r="I41" t="n">
         <v>1269.045864329446</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.84</v>
+        <v>-6.61</v>
       </c>
       <c r="L41" t="n">
-        <v>7.55</v>
+        <v>8.01</v>
       </c>
       <c r="M41" t="n">
         <v>0.92</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>7.37</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H42" t="n">
-        <v>1253.7</v>
+        <v>1192.25</v>
       </c>
       <c r="I42" t="n">
         <v>1202.252236501853</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.35</v>
+        <v>-6.19</v>
       </c>
       <c r="L42" t="n">
-        <v>2.54</v>
+        <v>6.76</v>
       </c>
       <c r="M42" t="n">
-        <v>0.38</v>
+        <v>1.89</v>
       </c>
       <c r="N42" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="O42" t="n">
         <v>1.69</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>10.32</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H43" t="n">
-        <v>1270.75</v>
+        <v>1296.4</v>
       </c>
       <c r="I43" t="n">
         <v>1274.286015093395</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K43" t="n">
-        <v>-6.58</v>
+        <v>-8.74</v>
       </c>
       <c r="L43" t="n">
-        <v>8.16</v>
+        <v>11.13</v>
       </c>
       <c r="M43" t="n">
         <v>2.99</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>10.26</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H44" t="n">
-        <v>1230.95</v>
+        <v>1144.65</v>
       </c>
       <c r="I44" t="n">
         <v>1200.161910345246</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K44" t="n">
-        <v>-5.05</v>
+        <v>-11.71</v>
       </c>
       <c r="L44" t="n">
-        <v>6.05</v>
+        <v>12.35</v>
       </c>
       <c r="M44" t="n">
         <v>2.04</v>
       </c>
       <c r="N44" t="n">
-        <v>4.37</v>
+        <v>7.01</v>
       </c>
       <c r="O44" t="n">
         <v>2.02</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>15.02</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44760</v>
+        <v>44761</v>
       </c>
       <c r="H45" t="n">
-        <v>1034.7</v>
+        <v>1052.85</v>
       </c>
       <c r="I45" t="n">
         <v>1041.214324298825</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K45" t="n">
-        <v>9.609999999999999</v>
+        <v>8.02</v>
       </c>
       <c r="L45" t="n">
         <v>8.31</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44817</v>
+        <v>44818</v>
       </c>
       <c r="H46" t="n">
-        <v>970.15</v>
+        <v>955.35</v>
       </c>
       <c r="I46" t="n">
         <v>957.1313819303083</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K46" t="n">
-        <v>-7.85</v>
+        <v>-9.26</v>
       </c>
       <c r="L46" t="n">
         <v>11.43</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.7</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44956</v>
+        <v>44957</v>
       </c>
       <c r="H47" t="n">
-        <v>774.95</v>
+        <v>802.65</v>
       </c>
       <c r="I47" t="n">
         <v>796.2776395612183</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K47" t="n">
-        <v>18.88</v>
+        <v>15.98</v>
       </c>
       <c r="L47" t="n">
         <v>1.27</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>6</v>
+      </c>
+      <c r="U47" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45002</v>
+        <v>45005</v>
       </c>
       <c r="H48" t="n">
-        <v>880.55</v>
+        <v>850.95</v>
       </c>
       <c r="I48" t="n">
         <v>852.8545586653023</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K48" t="n">
-        <v>9.710000000000001</v>
+        <v>6.02</v>
       </c>
       <c r="L48" t="n">
         <v>3.17</v>
@@ -3177,7 +3752,7 @@
         <v>2.98</v>
       </c>
       <c r="N48" t="n">
-        <v>2.31</v>
+        <v>3.36</v>
       </c>
       <c r="O48" t="n">
         <v>3.57</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>10.76</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45138</v>
+        <v>45139</v>
       </c>
       <c r="H49" t="n">
-        <v>780.1</v>
+        <v>797.4</v>
       </c>
       <c r="I49" t="n">
         <v>786.3595891275129</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K49" t="n">
-        <v>8.33</v>
+        <v>6.29</v>
       </c>
       <c r="L49" t="n">
         <v>4.24</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>6</v>
+      </c>
+      <c r="U49" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>5.94</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45205</v>
+        <v>45208</v>
       </c>
       <c r="H50" t="n">
-        <v>885.1</v>
+        <v>852.9</v>
       </c>
       <c r="I50" t="n">
         <v>859.4677810079901</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K50" t="n">
-        <v>11</v>
+        <v>6.96</v>
       </c>
       <c r="L50" t="n">
         <v>2.15</v>
       </c>
       <c r="M50" t="n">
-        <v>0.97</v>
+        <v>1.48</v>
       </c>
       <c r="N50" t="n">
-        <v>3.51</v>
+        <v>3.64</v>
       </c>
       <c r="O50" t="n">
         <v>2.22</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="H51" t="n">
-        <v>845.05</v>
+        <v>866.05</v>
       </c>
       <c r="I51" t="n">
         <v>866.0153722363933</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K51" t="n">
-        <v>0.92</v>
+        <v>-1.54</v>
       </c>
       <c r="L51" t="n">
         <v>3.41</v>
@@ -3348,7 +3959,7 @@
         <v>1.02</v>
       </c>
       <c r="N51" t="n">
-        <v>1.85</v>
+        <v>2.49</v>
       </c>
       <c r="O51" t="n">
         <v>-3.64</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>7.97</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45419</v>
+        <v>45420</v>
       </c>
       <c r="H52" t="n">
-        <v>1389.2</v>
+        <v>1318.8</v>
       </c>
       <c r="I52" t="n">
         <v>1381.272061862414</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K52" t="n">
-        <v>60.41</v>
+        <v>52.28</v>
       </c>
       <c r="L52" t="n">
         <v>3.8</v>
       </c>
       <c r="M52" t="n">
-        <v>1.56</v>
+        <v>7.86</v>
       </c>
       <c r="N52" t="n">
-        <v>4.03</v>
+        <v>5.07</v>
       </c>
       <c r="O52" t="n">
         <v>2.49</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>6</v>
+      </c>
+      <c r="U52" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>10.08</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c r="H53" t="n">
-        <v>1371.55</v>
+        <v>1411.15</v>
       </c>
       <c r="I53" t="n">
         <v>1405.385743335573</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K53" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="L53" t="n">
-        <v>4.83</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="M53" t="n">
         <v>0.87</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>10.18</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H54" t="n">
-        <v>1809.6</v>
+        <v>1757.2</v>
       </c>
       <c r="I54" t="n">
         <v>1789.312003287847</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K54" t="n">
-        <v>28.24</v>
+        <v>24.52</v>
       </c>
       <c r="L54" t="n">
         <v>12.16</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>6</v>
+      </c>
+      <c r="U54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>9.5</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="H55" t="n">
-        <v>1787.65</v>
+        <v>1807.5</v>
       </c>
       <c r="I55" t="n">
         <v>1803.798196116391</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.73</v>
+        <v>-2.86</v>
       </c>
       <c r="L55" t="n">
         <v>8.24</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>8.91</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45649</v>
+        <v>45650</v>
       </c>
       <c r="H56" t="n">
-        <v>1695.55</v>
+        <v>1675</v>
       </c>
       <c r="I56" t="n">
         <v>1683.526285916993</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K56" t="n">
-        <v>-6.19</v>
+        <v>-7.33</v>
       </c>
       <c r="L56" t="n">
-        <v>7.1</v>
+        <v>7.69</v>
       </c>
       <c r="M56" t="n">
         <v>0.57</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45657</v>
+        <v>45658</v>
       </c>
       <c r="H57" t="n">
-        <v>1789.95</v>
+        <v>1826.95</v>
       </c>
       <c r="I57" t="n">
         <v>1815.480322885987</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K57" t="n">
-        <v>-6.86</v>
+        <v>-9.07</v>
       </c>
       <c r="L57" t="n">
-        <v>7.99</v>
+        <v>9.43</v>
       </c>
       <c r="M57" t="n">
         <v>0.26</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>10.61</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="H58" t="n">
-        <v>1727.9</v>
+        <v>1663.5</v>
       </c>
       <c r="I58" t="n">
         <v>1679.153530162633</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.42</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>6.55</v>
+        <v>9.41</v>
       </c>
       <c r="M58" t="n">
         <v>0.53</v>
       </c>
       <c r="N58" t="n">
-        <v>2.67</v>
+        <v>3.73</v>
       </c>
       <c r="O58" t="n">
         <v>2.07</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>11.8</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45727</v>
+        <v>45728</v>
       </c>
       <c r="H59" t="n">
-        <v>1406.1</v>
+        <v>1445.45</v>
       </c>
       <c r="I59" t="n">
         <v>1424.501168774724</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K59" t="n">
-        <v>15.47</v>
+        <v>13.11</v>
       </c>
       <c r="L59" t="n">
         <v>4.08</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>11.47</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45748</v>
+        <v>45749</v>
       </c>
       <c r="H60" t="n">
-        <v>1352.05</v>
+        <v>1344.8</v>
       </c>
       <c r="I60" t="n">
         <v>1348.688729508214</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K60" t="n">
-        <v>-6.46</v>
+        <v>-6.96</v>
       </c>
       <c r="L60" t="n">
-        <v>6.75</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M60" t="n">
         <v>1.97</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>10.93</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45817</v>
+        <v>45818</v>
       </c>
       <c r="H61" t="n">
-        <v>1286.5</v>
+        <v>1317.7</v>
       </c>
       <c r="I61" t="n">
         <v>1305.506070968162</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K61" t="n">
-        <v>4.34</v>
+        <v>2.02</v>
       </c>
       <c r="L61" t="n">
         <v>1.45</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="H62" t="n">
-        <v>1344</v>
+        <v>1315.6</v>
       </c>
       <c r="I62" t="n">
         <v>1317.697792281486</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K62" t="n">
-        <v>2</v>
+        <v>-0.16</v>
       </c>
       <c r="L62" t="n">
         <v>5.4</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>6.88</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45883</v>
+        <v>45887</v>
       </c>
       <c r="H63" t="n">
-        <v>1274.8</v>
+        <v>1349.2</v>
       </c>
       <c r="I63" t="n">
         <v>1333.617124493233</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K63" t="n">
-        <v>3.1</v>
+        <v>-2.55</v>
       </c>
       <c r="L63" t="n">
-        <v>2.52</v>
+        <v>6.58</v>
       </c>
       <c r="M63" t="n">
-        <v>0.39</v>
+        <v>4.95</v>
       </c>
       <c r="N63" t="n">
-        <v>2.5</v>
+        <v>5.84</v>
       </c>
       <c r="O63" t="n">
         <v>-2.11</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="H64" t="n">
-        <v>1359.4</v>
+        <v>1292.4</v>
       </c>
       <c r="I64" t="n">
         <v>1347.190287130431</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K64" t="n">
-        <v>0.76</v>
+        <v>-4.21</v>
       </c>
       <c r="L64" t="n">
-        <v>1.72</v>
+        <v>4.53</v>
       </c>
       <c r="M64" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N64" t="n">
-        <v>3.08</v>
+        <v>4.93</v>
       </c>
       <c r="O64" t="n">
         <v>5.84</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4</v>
+      </c>
+      <c r="U64" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>11.63</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="H65" t="n">
-        <v>1384.3</v>
+        <v>1430.2</v>
       </c>
       <c r="I65" t="n">
         <v>1416.253477841235</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K65" t="n">
-        <v>-7.11</v>
+        <v>-10.66</v>
       </c>
       <c r="L65" t="n">
-        <v>10.33</v>
+        <v>12.01</v>
       </c>
       <c r="M65" t="n">
         <v>0.42</v>
       </c>
       <c r="N65" t="n">
-        <v>2.59</v>
+        <v>3.32</v>
       </c>
       <c r="O65" t="n">
         <v>-4.93</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>8.06</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H66" t="n">
-        <v>1398.4</v>
+        <v>1324.3</v>
       </c>
       <c r="I66" t="n">
         <v>1388.846003862638</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.22</v>
+        <v>-7.4</v>
       </c>
       <c r="L66" t="n">
-        <v>3.03</v>
+        <v>7.76</v>
       </c>
       <c r="M66" t="n">
-        <v>0.44</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N66" t="n">
-        <v>2.55</v>
+        <v>5.3</v>
       </c>
       <c r="O66" t="n">
         <v>3.32</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>11.67</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H67" t="n">
-        <v>1366.9</v>
+        <v>1419.5</v>
       </c>
       <c r="I67" t="n">
         <v>1416.428786703702</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.22</v>
+        <v>-7.19</v>
       </c>
       <c r="L67" t="n">
-        <v>5.9</v>
+        <v>7.76</v>
       </c>
       <c r="M67" t="n">
         <v>1.82</v>
       </c>
       <c r="N67" t="n">
-        <v>3.18</v>
+        <v>3.85</v>
       </c>
       <c r="O67" t="n">
         <v>-5.3</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>12.96</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="H68" t="n">
-        <v>1449.4</v>
+        <v>1414.2</v>
       </c>
       <c r="I68" t="n">
         <v>1430.36472198269</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K68" t="n">
-        <v>2.11</v>
+        <v>-0.37</v>
       </c>
       <c r="L68" t="n">
         <v>4.18</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>11.12</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="H69" t="n">
-        <v>1402.2</v>
+        <v>1408.8</v>
       </c>
       <c r="I69" t="n">
         <v>1405.864064186152</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K69" t="n">
-        <v>0.85</v>
+        <v>0.38</v>
       </c>
       <c r="L69" t="n">
         <v>2.45</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>12.4</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="H70" t="n">
-        <v>1363.9</v>
+        <v>1324.8</v>
       </c>
       <c r="I70" t="n">
         <v>1361.741299454879</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.19</v>
+        <v>-5.96</v>
       </c>
       <c r="L70" t="n">
-        <v>4.01</v>
+        <v>6.23</v>
       </c>
       <c r="M70" t="n">
         <v>0.38</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>12.99</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="H71" t="n">
-        <v>1327.6</v>
+        <v>1352.9</v>
       </c>
       <c r="I71" t="n">
         <v>1352.775444475094</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.21</v>
+        <v>-2.12</v>
       </c>
       <c r="L71" t="n">
-        <v>2.88</v>
+        <v>4.3</v>
       </c>
       <c r="M71" t="n">
         <v>1.91</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>9.48</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="H72" t="n">
-        <v>1300.5</v>
+        <v>1275</v>
       </c>
       <c r="I72" t="n">
         <v>1276.453165258812</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K72" t="n">
-        <v>-3.87</v>
+        <v>-5.76</v>
       </c>
       <c r="L72" t="n">
         <v>7.83</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4605,6 +5480,14 @@
       <c r="Q73" t="n">
         <v>57</v>
       </c>
+      <c r="R73" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9563,7 +10446,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.9</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="6">
@@ -9573,7 +10456,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -9583,7 +10466,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8">
@@ -9593,7 +10476,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -9603,7 +10486,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="10">
@@ -9613,7 +10496,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11">
@@ -9623,7 +10506,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -9633,7 +10516,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -9643,7 +10526,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33.8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -9653,7 +10536,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.3</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="15">
@@ -9663,7 +10546,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.42</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="16">
@@ -9673,7 +10556,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="17">
@@ -9683,7 +10566,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>82.44</v>
+        <v>77.58</v>
       </c>
     </row>
     <row r="18">
@@ -9693,7 +10576,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.1</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="19">
@@ -9703,7 +10586,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.48</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="20">
@@ -9713,7 +10596,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.18</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="21">
@@ -9723,7 +10606,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12.49</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="22">
@@ -9733,7 +10616,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -9743,7 +10626,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -9753,7 +10636,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.59</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="25">
@@ -9763,7 +10646,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.42</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="26">
@@ -9773,7 +10656,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.79</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="27">
@@ -9783,7 +10666,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.31</v>
+        <v>12.42</v>
       </c>
     </row>
     <row r="28">
@@ -9793,7 +10676,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
